--- a/Доработки функционала.xlsx
+++ b/Доработки функционала.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loger\OneDrive\Документы\GitHub\PostManager\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\PostManager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C046BE9-2064-4585-8418-B4FCF70333EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D7B036-B5C3-4238-B238-463C0B815FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,15 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="28">
   <si>
     <t>Тип задачи</t>
   </si>
@@ -96,6 +93,24 @@
   </si>
   <si>
     <t>Сохранять последнюю активную вкладку</t>
+  </si>
+  <si>
+    <t>Убрать автозадачу по плану</t>
+  </si>
+  <si>
+    <t>Не выкачивается файл с блока</t>
+  </si>
+  <si>
+    <t>Группировка схем</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>v 3.7.2</t>
   </si>
 </sst>
 </file>
@@ -140,30 +155,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
     <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -185,15 +203,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CED37E04-3089-429F-8FC7-9488ABCDC89C}" name="Таблица1" displayName="Таблица1" ref="A1:F48" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CED37E04-3089-429F-8FC7-9488ABCDC89C}" name="Таблица1" displayName="Таблица1" ref="A1:F48" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="A1:F48" xr:uid="{CED37E04-3089-429F-8FC7-9488ABCDC89C}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{63A868A4-160C-4172-808C-D76ED4783EBD}" name="№" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{F4ED38AF-F319-40EA-AAB3-248CB87B7AFC}" name="Тип задачи" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{D8BDB838-EA23-4840-B64D-56289F1E4F12}" name="Описание" dataDxfId="0"/>
-    <tableColumn id="8" xr3:uid="{92A1F7A0-6B3C-449B-A608-DD98F94E2FDD}" name="Вкладка" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{D671CC31-6BB9-4AE9-A985-63483BD37EF1}" name="Статус" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{52F352BB-35BC-47B2-9B70-5EDF5BB7EB43}" name="Версия коммита"/>
+    <tableColumn id="1" xr3:uid="{63A868A4-160C-4172-808C-D76ED4783EBD}" name="№" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{F4ED38AF-F319-40EA-AAB3-248CB87B7AFC}" name="Тип задачи" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{D8BDB838-EA23-4840-B64D-56289F1E4F12}" name="Описание" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{92A1F7A0-6B3C-449B-A608-DD98F94E2FDD}" name="Вкладка" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{D671CC31-6BB9-4AE9-A985-63483BD37EF1}" name="Статус" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{52F352BB-35BC-47B2-9B70-5EDF5BB7EB43}" name="Версия коммита" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -463,27 +481,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39" style="5" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="22.88671875" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39" style="4" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -493,309 +511,375 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E4" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E5" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E6" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E7" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E8" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -823,33 +907,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{293D6175-44B4-43F2-B5CD-9AE0990F4253}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B1" s="5"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>

--- a/Доработки функционала.xlsx
+++ b/Доработки функционала.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\PostManager\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loger\OneDrive\Документы\GitHub\PostManager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D7B036-B5C3-4238-B238-463C0B815FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFF1675-0991-4EE7-B4B0-72248C57F920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="36">
   <si>
     <t>Тип задачи</t>
   </si>
@@ -68,9 +71,6 @@
   </si>
   <si>
     <t>Удалить все ненужные либы</t>
-  </si>
-  <si>
-    <t>Автоматически создавать первоначальную вкладку</t>
   </si>
   <si>
     <t>Вкладка</t>
@@ -111,6 +111,33 @@
   </si>
   <si>
     <t>v 3.7.2</t>
+  </si>
+  <si>
+    <t>Создается дополнительный блок при соединении 2х блоков</t>
+  </si>
+  <si>
+    <t>Ограничить отображение текста в блоках до 100 символов</t>
+  </si>
+  <si>
+    <t>Слетает привязка к точке</t>
+  </si>
+  <si>
+    <t>Возможное решение</t>
+  </si>
+  <si>
+    <t>Новое поле в БД</t>
+  </si>
+  <si>
+    <t>Создание выпадающего меню с созданием папки и схемы в папке</t>
+  </si>
+  <si>
+    <t>Добавить проверку создания линии</t>
+  </si>
+  <si>
+    <t>Убрать автоматическую смену точки привязки</t>
+  </si>
+  <si>
+    <t>v 3.7.3</t>
   </si>
 </sst>
 </file>
@@ -167,7 +194,7 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -176,6 +203,9 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -203,12 +233,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CED37E04-3089-429F-8FC7-9488ABCDC89C}" name="Таблица1" displayName="Таблица1" ref="A1:F48" totalsRowShown="0" headerRowDxfId="6">
-  <autoFilter ref="A1:F48" xr:uid="{CED37E04-3089-429F-8FC7-9488ABCDC89C}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{63A868A4-160C-4172-808C-D76ED4783EBD}" name="№" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{F4ED38AF-F319-40EA-AAB3-248CB87B7AFC}" name="Тип задачи" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{D8BDB838-EA23-4840-B64D-56289F1E4F12}" name="Описание" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CED37E04-3089-429F-8FC7-9488ABCDC89C}" name="Таблица1" displayName="Таблица1" ref="A1:G48" totalsRowShown="0" headerRowDxfId="7">
+  <autoFilter ref="A1:G48" xr:uid="{CED37E04-3089-429F-8FC7-9488ABCDC89C}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{63A868A4-160C-4172-808C-D76ED4783EBD}" name="№" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{F4ED38AF-F319-40EA-AAB3-248CB87B7AFC}" name="Тип задачи" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{D8BDB838-EA23-4840-B64D-56289F1E4F12}" name="Описание" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{5C3F698C-2F33-4D6B-8C6A-B546D7BED6E3}" name="Возможное решение" dataDxfId="3"/>
     <tableColumn id="8" xr3:uid="{92A1F7A0-6B3C-449B-A608-DD98F94E2FDD}" name="Вкладка" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{D671CC31-6BB9-4AE9-A985-63483BD37EF1}" name="Статус" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{52F352BB-35BC-47B2-9B70-5EDF5BB7EB43}" name="Версия коммита" dataDxfId="0"/>
@@ -480,18 +511,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G48"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="39" style="4" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
@@ -502,16 +534,19 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -521,17 +556,17 @@
       <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -541,17 +576,17 @@
       <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -561,14 +596,14 @@
       <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -578,14 +613,14 @@
       <c r="C5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -595,14 +630,14 @@
       <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -610,276 +645,321 @@
         <v>10</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="F7" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -896,7 +976,7 @@
           <x14:formula1>
             <xm:f>Легенда!$A$2:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B48</xm:sqref>
+          <xm:sqref>B16:B48 B2:B14</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -907,33 +987,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{293D6175-44B4-43F2-B5CD-9AE0990F4253}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
